--- a/data/stx_xlsx/TEL2b.ST.xlsx
+++ b/data/stx_xlsx/TEL2b.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="622">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1270,6 +1270,9 @@
   </si>
   <si>
     <t>Interest-bearing liabilities - Balancing value</t>
+  </si>
+  <si>
+    <t>Interest Bearing Liabilities (Do not use)</t>
   </si>
   <si>
     <t>Other-interest-bearing liabilities - Balancing value</t>
@@ -20902,8 +20905,8 @@
       <c r="W164" s="15"/>
     </row>
     <row r="165" ht="15.0" customHeight="1">
-      <c r="A165" s="14" t="s">
-        <v>382</v>
+      <c r="A165" s="29" t="s">
+        <v>417</v>
       </c>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -20958,7 +20961,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -20991,7 +20994,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -21161,7 +21164,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B171" s="19">
         <v>3711.23</v>
@@ -21220,7 +21223,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B172" s="19">
         <v>120.28</v>
@@ -21261,7 +21264,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -21304,7 +21307,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="18">
@@ -21335,7 +21338,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B175" s="17">
         <v>29986.14</v>
@@ -21406,7 +21409,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B176" s="19">
         <v>545.64</v>
@@ -21439,7 +21442,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B177" s="17">
         <v>44410.06</v>
@@ -21510,7 +21513,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B178" s="19">
         <v>951.32</v>
@@ -21577,7 +21580,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B179" s="15">
         <v>29936.93</v>
@@ -21707,7 +21710,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -21760,7 +21763,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B182" s="20">
         <v>-360.84</v>
@@ -21817,7 +21820,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B183" s="19">
         <v>426.45</v>
@@ -21864,7 +21867,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B184" s="20">
         <v>-6606.73</v>
@@ -21931,7 +21934,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B185" s="18">
         <v>1.09</v>
@@ -21968,7 +21971,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B186" s="17">
         <v>24348.22</v>
@@ -22100,7 +22103,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="16" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
@@ -22161,7 +22164,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -22190,7 +22193,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="16" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B190" s="17">
         <v>24348.22</v>
@@ -22261,7 +22264,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B191" s="21">
         <v>-1.09</v>
@@ -22296,7 +22299,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="16" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B192" s="17">
         <v>68757.18</v>
@@ -22367,7 +22370,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B193" s="19">
         <v>696.22</v>
@@ -22438,7 +22441,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B194" s="18">
         <v>2.67</v>
@@ -22509,7 +22512,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B195" s="19">
         <v>693.56</v>
@@ -22580,7 +22583,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
@@ -22639,7 +22642,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -22674,7 +22677,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -22703,7 +22706,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -22734,7 +22737,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B200" s="15"/>
       <c r="C200" s="19">
@@ -22783,7 +22786,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B201" s="15"/>
       <c r="C201" s="19">
@@ -22844,7 +22847,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B202" s="15"/>
       <c r="C202" s="19">
@@ -22907,7 +22910,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B203" s="15"/>
       <c r="C203" s="19">
@@ -22970,7 +22973,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B204" s="15"/>
       <c r="C204" s="19">
@@ -23033,7 +23036,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B205" s="15"/>
       <c r="C205" s="19">
@@ -23096,7 +23099,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B206" s="15"/>
       <c r="C206" s="19">
@@ -23159,7 +23162,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -23214,7 +23217,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -23245,7 +23248,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -23274,7 +23277,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -23309,7 +23312,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B211" s="15"/>
       <c r="C211" s="19">
@@ -23366,7 +23369,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B212" s="15"/>
       <c r="C212" s="18">
@@ -23423,7 +23426,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B213" s="15"/>
       <c r="C213" s="19">
@@ -23480,7 +23483,7 @@
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B214" s="15"/>
       <c r="C214" s="19">
@@ -23537,7 +23540,7 @@
     </row>
     <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B215" s="15"/>
       <c r="C215" s="19">
@@ -23594,7 +23597,7 @@
     </row>
     <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B216" s="15"/>
       <c r="C216" s="19">
@@ -23633,7 +23636,7 @@
     </row>
     <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" s="15"/>
       <c r="C217" s="19">
@@ -23672,7 +23675,7 @@
     </row>
     <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B218" s="15"/>
       <c r="C218" s="19">
@@ -23719,7 +23722,7 @@
     </row>
     <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B219" s="27"/>
       <c r="C219" s="27"/>
@@ -23762,7 +23765,7 @@
     </row>
     <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B220" s="18">
         <v>9.82</v>
@@ -23833,7 +23836,7 @@
     </row>
     <row r="221" ht="15.0" customHeight="1">
       <c r="A221" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B221" s="18">
         <v>9.82</v>
@@ -23904,7 +23907,7 @@
     </row>
     <row r="222" ht="15.0" customHeight="1">
       <c r="A222" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B222" s="18">
         <v>0.01</v>
@@ -23975,7 +23978,7 @@
     </row>
     <row r="223" ht="15.0" customHeight="1">
       <c r="A223" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B223" s="18">
         <v>9.82</v>
@@ -24028,7 +24031,7 @@
     </row>
     <row r="224" ht="15.0" customHeight="1">
       <c r="A224" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B224" s="18">
         <v>9.82</v>
@@ -24077,7 +24080,7 @@
     </row>
     <row r="225" ht="15.0" customHeight="1">
       <c r="A225" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B225" s="19">
         <v>684.3</v>
@@ -24148,7 +24151,7 @@
     </row>
     <row r="226" ht="15.0" customHeight="1">
       <c r="A226" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B226" s="18">
         <v>0.57</v>
@@ -24217,7 +24220,7 @@
     </row>
     <row r="227" ht="15.0" customHeight="1">
       <c r="A227" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B227" s="18">
         <v>0.99</v>
@@ -24288,7 +24291,7 @@
     </row>
     <row r="228" ht="15.0" customHeight="1">
       <c r="A228" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B228" s="19">
         <v>683.74</v>
@@ -24359,7 +24362,7 @@
     </row>
     <row r="229" ht="15.0" customHeight="1">
       <c r="A229" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B229" s="19">
         <v>683.74</v>
@@ -24412,7 +24415,7 @@
     </row>
     <row r="230" ht="15.0" customHeight="1">
       <c r="A230" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B230" s="18">
         <v>0.57</v>
@@ -24465,7 +24468,7 @@
     </row>
     <row r="231" ht="15.0" customHeight="1">
       <c r="A231" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B231" s="19">
         <v>684.3</v>
@@ -24518,7 +24521,7 @@
     </row>
     <row r="232" ht="15.0" customHeight="1">
       <c r="A232" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B232" s="18">
         <v>2.1</v>
@@ -24583,7 +24586,7 @@
     </row>
     <row r="233" ht="15.0" customHeight="1">
       <c r="A233" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B233" s="18">
         <v>2.1</v>
@@ -25434,7 +25437,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25820,70 +25823,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -25959,7 +25962,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -26057,7 +26060,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -26086,7 +26089,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="19">
@@ -26121,7 +26124,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B22" s="19">
         <v>1164.02</v>
@@ -26166,7 +26169,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B23" s="19">
         <v>101.68</v>
@@ -26195,7 +26198,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="21">
@@ -26238,7 +26241,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -26279,7 +26282,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B26" s="18">
         <v>32.83</v>
@@ -26318,7 +26321,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -26357,7 +26360,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -26396,7 +26399,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B29" s="19">
         <v>4858.38</v>
@@ -26443,7 +26446,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -26502,7 +26505,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -26549,7 +26552,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B32" s="19">
         <v>6555.16</v>
@@ -26610,7 +26613,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B33" s="19">
         <v>992.44</v>
@@ -26679,7 +26682,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -26726,7 +26729,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="18">
@@ -26858,7 +26861,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="19">
@@ -26911,7 +26914,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="18">
@@ -26964,7 +26967,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="18">
@@ -27017,7 +27020,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B40" s="20">
         <v>-949.01</v>
@@ -27072,7 +27075,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B41" s="20">
         <v>-1043.28</v>
@@ -27127,7 +27130,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -27158,7 +27161,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B43" s="19">
         <v>303.98</v>
@@ -27199,7 +27202,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -27246,7 +27249,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -27493,7 +27496,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="21">
@@ -27669,7 +27672,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="18">
@@ -27755,7 +27758,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B56" s="21">
         <v>-2.12</v>
@@ -27794,7 +27797,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B57" s="17">
         <v>12014.08</v>
@@ -27865,7 +27868,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="20">
@@ -27932,7 +27935,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -27989,7 +27992,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="20">
@@ -28028,7 +28031,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B61" s="20">
         <v>-3911.49</v>
@@ -28087,7 +28090,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="18">
@@ -28154,7 +28157,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -28183,7 +28186,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -28216,7 +28219,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -28245,7 +28248,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -28310,7 +28313,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B67" s="18">
         <v>2.12</v>
@@ -28381,7 +28384,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="18">
@@ -28428,7 +28431,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -28542,7 +28545,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -28571,7 +28574,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B72" s="18">
         <v>19.06</v>
@@ -28632,7 +28635,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -28661,7 +28664,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -28698,7 +28701,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -28729,7 +28732,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B76" s="18">
         <v>1.06</v>
@@ -28764,7 +28767,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -28795,7 +28798,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B78" s="24">
         <v>-3889.25</v>
@@ -28866,7 +28869,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="19">
@@ -28929,7 +28932,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="20">
@@ -28982,7 +28985,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="20">
@@ -29029,7 +29032,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="19">
@@ -29088,7 +29091,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -29129,7 +29132,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B84" s="20">
         <v>-4663.49</v>
@@ -29198,7 +29201,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B85" s="20">
         <v>-5145.41</v>
@@ -29227,7 +29230,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B86" s="19">
         <v>3174.31</v>
@@ -29256,7 +29259,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -29295,7 +29298,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B88" s="20">
         <v>-1542.14</v>
@@ -29356,7 +29359,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -29401,7 +29404,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -29430,7 +29433,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -29467,7 +29470,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -29496,7 +29499,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -29543,7 +29546,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -29582,7 +29585,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -29613,7 +29616,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -29650,7 +29653,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -29679,7 +29682,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="16" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B98" s="24">
         <v>-8176.74</v>
@@ -29750,7 +29753,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B99" s="21">
         <v>-20.12</v>
@@ -29821,7 +29824,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B100" s="19">
         <v>346.63</v>
@@ -29892,7 +29895,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B101" s="19">
         <v>272.27</v>
@@ -29963,7 +29966,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B102" s="21">
         <v>-51.9</v>
@@ -30018,7 +30021,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="16" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B103" s="25">
         <v>-72.02</v>
@@ -30089,7 +30092,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -30130,7 +30133,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -30171,7 +30174,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B106" s="19">
         <v>6562.57</v>
@@ -31125,7 +31128,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -31298,31 +31301,31 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -31802,7 +31805,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -31903,36 +31906,36 @@
         <v>71</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="30" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -31967,7 +31970,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="32" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B21" s="33">
         <v>108981.3</v>
@@ -32060,7 +32063,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B22" s="33">
         <v>101361.95</v>
@@ -32145,7 +32148,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
@@ -32180,7 +32183,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="32" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B24" s="33">
         <v>77848.51</v>
@@ -32273,7 +32276,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="32" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B25" s="33">
         <v>70536.56</v>
@@ -32358,7 +32361,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="30" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -32393,7 +32396,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="32" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B27" s="34">
         <v>112.32</v>
@@ -32486,7 +32489,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="32" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B28" s="34">
         <v>101.91</v>
@@ -32571,7 +32574,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="30" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -32606,7 +32609,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="32" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B30" s="36">
         <v>7.63</v>
@@ -32699,7 +32702,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B31" s="36">
         <v>8.56</v>
@@ -32784,7 +32787,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="30" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -32819,7 +32822,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B33" s="36">
         <v>4.42</v>
@@ -32912,7 +32915,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="32" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B34" s="36">
         <v>4.51</v>
@@ -32997,7 +33000,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="32" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B35" s="36">
         <v>6.32</v>
@@ -33090,7 +33093,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="32" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B36" s="36">
         <v>6.45</v>
@@ -33175,7 +33178,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -33210,7 +33213,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="32" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B38" s="35">
         <v>3.42</v>
@@ -33303,7 +33306,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="32" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B39" s="35">
         <v>2.58</v>
@@ -33388,7 +33391,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -33423,7 +33426,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B41" s="33"/>
       <c r="C41" s="33"/>
@@ -33500,7 +33503,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B42" s="33"/>
       <c r="C42" s="33"/>
@@ -33573,7 +33576,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -33608,7 +33611,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B44" s="35">
         <v>2.57</v>
@@ -33701,7 +33704,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="32" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B45" s="35">
         <v>2.46</v>
@@ -33786,7 +33789,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
@@ -33821,7 +33824,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="32" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B47" s="35">
         <v>13.11</v>
@@ -33898,7 +33901,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="32" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B48" s="35">
         <v>11.69</v>
@@ -33977,7 +33980,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="30" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
@@ -34012,7 +34015,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="32" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B50" s="35">
         <v>7.78</v>
@@ -34105,7 +34108,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="32" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B51" s="35">
         <v>6.44</v>
@@ -34190,7 +34193,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
@@ -34225,7 +34228,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B53" s="35">
         <v>19.66</v>
@@ -34312,7 +34315,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="32" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B54" s="35">
         <v>14.11</v>
@@ -34397,7 +34400,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
@@ -34432,7 +34435,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="32" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B56" s="35">
         <v>19.02</v>
@@ -34521,7 +34524,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="32" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B57" s="35">
         <v>2.58</v>
@@ -34606,7 +34609,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
@@ -34641,7 +34644,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="32" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B59" s="35">
         <v>5.65</v>
@@ -34728,7 +34731,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="32" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B60" s="35">
         <v>1.3</v>
@@ -34801,7 +34804,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -34836,7 +34839,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="32" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B62" s="35">
         <v>3.58</v>
@@ -34929,7 +34932,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="32" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B63" s="35">
         <v>3.52</v>
@@ -35014,7 +35017,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
@@ -35049,7 +35052,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="32" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B65" s="35">
         <v>8.87</v>
@@ -35138,7 +35141,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="32" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B66" s="35">
         <v>8.79</v>
@@ -35215,7 +35218,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="30" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -35250,7 +35253,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="32" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B68" s="35">
         <v>10.84</v>
@@ -35343,7 +35346,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="32" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B69" s="35">
         <v>10.45</v>
@@ -35428,7 +35431,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="30" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -35463,7 +35466,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="32" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B71" s="35">
         <v>18.27</v>
@@ -35540,7 +35543,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="32" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B72" s="35">
         <v>16.73</v>
